--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131140294</v>
       </c>
       <c r="B2" t="n">
-        <v>57897</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>131140313</v>
       </c>
       <c r="B3" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131140294</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>131140313</v>
       </c>
       <c r="B3" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131140294</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>131140313</v>
       </c>
       <c r="B3" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131140294</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>131140313</v>
       </c>
       <c r="B3" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131140294</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>131140313</v>
       </c>
       <c r="B3" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,6 +1034,129 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134265225</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>7 km markering milspåret, I2-skogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>410743</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6585832</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grava</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Willy Krönström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Willy Krönström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131140294</v>
       </c>
       <c r="B2" t="n">
-        <v>57911</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131140313</v>
+        <v>134265225</v>
       </c>
       <c r="B3" t="n">
-        <v>58270</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,30 +809,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -875,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +924,7 @@
         <v>131742830</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>57969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134265225</v>
+        <v>131140313</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,34 +1051,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1117,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55256-2021 artfynd.xlsx
+++ b/artfynd/A 55256-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131140294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134265225</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131742830</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,8 +1176,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131140313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>